--- a/assets/arithmos-modele-balance-detaillee.xlsx
+++ b/assets/arithmos-modele-balance-detaillee.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -89,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -99,6 +101,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -466,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -481,10 +484,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complétez uniquement les cellules en jaune (Société, Exercice, Solde). Colonne Solde = montant signé : positif si le compte est normalement débiteur, négatif s'il est normalement créditeur. Un fichier = un exercice (une année) d'une société. N'ajoutez pas de ligne de total.</t>
+          <t>Complétez uniquement les cellules en jaune (Société, Date de début, Date de fin, et la colonne Solde). Solde = montant signé : positif si le compte est normalement débiteur, négatif s'il est normalement créditeur. Un fichier = un exercice (une période) d'une société — peut être une année complète ou une période plus courte (ex. situation intermédiaire à 6 mois). N'ajoutez pas de ligne de total.</t>
         </is>
       </c>
     </row>
@@ -499,45 +502,50 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Exercice (année)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Libellé (facultatif)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Solde (EUR, signé)</t>
-        </is>
-      </c>
+          <t>Date de début</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Date de fin</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Libellé (facultatif)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Solde (EUR, signé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>EX</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Exemple (ligne fictive à ignorer) — ex. compte client</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>1000</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="C9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="4" t="n"/>
@@ -655,6 +663,9 @@
     </row>
     <row r="48">
       <c r="C48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
